--- a/artfynd/A 14214-2025 artfynd.xlsx
+++ b/artfynd/A 14214-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124965524</v>
+        <v>124965523</v>
       </c>
       <c r="B2" t="n">
         <v>57918</v>
@@ -710,15 +710,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662758</v>
+        <v>662703</v>
       </c>
       <c r="R2" t="n">
-        <v>6554533</v>
+        <v>6554544</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hål med bo</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124965523</v>
+        <v>124965524</v>
       </c>
       <c r="B3" t="n">
         <v>57918</v>
@@ -834,11 +835,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -847,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662703</v>
+        <v>662758</v>
       </c>
       <c r="R3" t="n">
-        <v>6554544</v>
+        <v>6554533</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hål med bo</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14214-2025 artfynd.xlsx
+++ b/artfynd/A 14214-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124965523</v>
+        <v>124965524</v>
       </c>
       <c r="B2" t="n">
         <v>57918</v>
@@ -710,11 +710,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662703</v>
+        <v>662758</v>
       </c>
       <c r="R2" t="n">
-        <v>6554544</v>
+        <v>6554533</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hål med bo</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124965524</v>
+        <v>124965523</v>
       </c>
       <c r="B3" t="n">
         <v>57918</v>
@@ -835,15 +834,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -852,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662758</v>
+        <v>662703</v>
       </c>
       <c r="R3" t="n">
-        <v>6554533</v>
+        <v>6554544</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hål med bo</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14214-2025 artfynd.xlsx
+++ b/artfynd/A 14214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124965524</v>
       </c>
       <c r="B2" t="n">
-        <v>57918</v>
+        <v>58026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>124965523</v>
       </c>
       <c r="B3" t="n">
-        <v>57918</v>
+        <v>58026</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 14214-2025 artfynd.xlsx
+++ b/artfynd/A 14214-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124965524</v>
+        <v>124965523</v>
       </c>
       <c r="B2" t="n">
-        <v>58026</v>
+        <v>58353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,15 +705,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662758</v>
+        <v>662703</v>
       </c>
       <c r="R2" t="n">
-        <v>6554533</v>
+        <v>6554544</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hål med bo</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124965523</v>
+        <v>124965524</v>
       </c>
       <c r="B3" t="n">
-        <v>58026</v>
+        <v>58353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,11 +825,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662703</v>
+        <v>662758</v>
       </c>
       <c r="R3" t="n">
-        <v>6554544</v>
+        <v>6554533</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hål med bo</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14214-2025 artfynd.xlsx
+++ b/artfynd/A 14214-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124965523</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,8 +921,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124965524</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>